--- a/游戏设计王/老虎机数学入门-PartI-计算模型.xlsx
+++ b/游戏设计王/老虎机数学入门-PartI-计算模型.xlsx
@@ -871,7 +871,7 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr9="http://schemas.microsoft.com/office/spreadsheetml/2016/revision9" mc:Ignorable="xr9">
-  <numFmts count="9">
+  <numFmts count="10">
     <numFmt numFmtId="41" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;_ ;_ @_ "/>
     <numFmt numFmtId="42" formatCode="_ &quot;￥&quot;* #,##0_ ;_ &quot;￥&quot;* \-#,##0_ ;_ &quot;￥&quot;* &quot;-&quot;_ ;_ @_ "/>
     <numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
@@ -881,6 +881,7 @@
     <numFmt numFmtId="178" formatCode="#,##0"/>
     <numFmt numFmtId="179" formatCode="0%"/>
     <numFmt numFmtId="180" formatCode="0.000%"/>
+    <numFmt numFmtId="181" formatCode="0.0000000000%"/>
   </numFmts>
   <fonts count="32">
     <font>
@@ -1615,7 +1616,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="84">
+  <cellXfs count="88">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
@@ -1802,6 +1803,10 @@
     <xf numFmtId="0" fontId="7" fillId="10" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
+    <xf numFmtId="181" applyNumberFormat="1" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="181" applyNumberFormat="1" fontId="6" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="181" applyNumberFormat="1" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="181" applyNumberFormat="1" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1"/>
   </cellXfs>
   <cellStyles count="49">
     <cellStyle name="常规" xfId="0" builtinId="0"/>
@@ -11055,7 +11060,7 @@
         <f t="shared" ref="S29:S44" si="2">INDEX($B$59:$D$64,MATCH($J29,$A$59:$A$64,0),MATCH($K29,$B$58:$D$58,0))</f>
         <v>50</v>
       </c>
-      <c r="T29" s="27">
+      <c r="T29" s="84">
         <f t="shared" ref="T29:T44" si="3">R29*S29</f>
         <v>0.16875</v>
       </c>
@@ -11155,7 +11160,7 @@
         <f t="shared" si="2"/>
         <v>100</v>
       </c>
-      <c r="T30" s="27">
+      <c r="T30" s="84">
         <f t="shared" si="3"/>
         <v>0.016</v>
       </c>
@@ -11255,7 +11260,7 @@
         <f t="shared" si="2"/>
         <v>30</v>
       </c>
-      <c r="T31" s="27">
+      <c r="T31" s="84">
         <f t="shared" si="3"/>
         <v>0.0192</v>
       </c>
@@ -11355,7 +11360,7 @@
         <f t="shared" si="2"/>
         <v>5</v>
       </c>
-      <c r="T32" s="27">
+      <c r="T32" s="84">
         <f t="shared" si="3"/>
         <v>0.016</v>
       </c>
@@ -11455,7 +11460,7 @@
         <f t="shared" si="2"/>
         <v>100</v>
       </c>
-      <c r="T33" s="27">
+      <c r="T33" s="84">
         <f t="shared" si="3"/>
         <v>0.024</v>
       </c>
@@ -11555,7 +11560,7 @@
         <f t="shared" si="2"/>
         <v>25</v>
       </c>
-      <c r="T34" s="27">
+      <c r="T34" s="84">
         <f t="shared" si="3"/>
         <v>0.024</v>
       </c>
@@ -11655,7 +11660,7 @@
         <f t="shared" si="2"/>
         <v>5</v>
       </c>
-      <c r="T35" s="27">
+      <c r="T35" s="84">
         <f t="shared" si="3"/>
         <v>0.024</v>
       </c>
@@ -11755,7 +11760,7 @@
         <f t="shared" si="2"/>
         <v>75</v>
       </c>
-      <c r="T36" s="27">
+      <c r="T36" s="84">
         <f t="shared" si="3"/>
         <v>0.0703125</v>
       </c>
@@ -11850,7 +11855,7 @@
         <f t="shared" si="2"/>
         <v>20</v>
       </c>
-      <c r="T37" s="27">
+      <c r="T37" s="84">
         <f t="shared" si="3"/>
         <v>0.05625</v>
       </c>
@@ -11945,7 +11950,7 @@
         <f t="shared" si="2"/>
         <v>5</v>
       </c>
-      <c r="T38" s="27">
+      <c r="T38" s="84">
         <f t="shared" si="3"/>
         <v>0.05625</v>
       </c>
@@ -12035,7 +12040,7 @@
         <f t="shared" si="2"/>
         <v>75</v>
       </c>
-      <c r="T39" s="27">
+      <c r="T39" s="84">
         <f t="shared" si="3"/>
         <v>0.05859375</v>
       </c>
@@ -12130,7 +12135,7 @@
         <f t="shared" si="2"/>
         <v>20</v>
       </c>
-      <c r="T40" s="27">
+      <c r="T40" s="84">
         <f t="shared" si="3"/>
         <v>0.046875</v>
       </c>
@@ -12225,7 +12230,7 @@
         <f t="shared" si="2"/>
         <v>5</v>
       </c>
-      <c r="T41" s="27">
+      <c r="T41" s="84">
         <f t="shared" si="3"/>
         <v>0.046875</v>
       </c>
@@ -12320,7 +12325,7 @@
         <f t="shared" si="2"/>
         <v>50</v>
       </c>
-      <c r="T42" s="27">
+      <c r="T42" s="84">
         <f t="shared" si="3"/>
         <v>0.0703125</v>
       </c>
@@ -12415,7 +12420,7 @@
         <f t="shared" si="2"/>
         <v>10</v>
       </c>
-      <c r="T43" s="27">
+      <c r="T43" s="84">
         <f t="shared" si="3"/>
         <v>0.0328125</v>
       </c>
@@ -12510,7 +12515,7 @@
         <f t="shared" si="2"/>
         <v>5</v>
       </c>
-      <c r="T44" s="27">
+      <c r="T44" s="84">
         <f t="shared" si="3"/>
         <v>0.0703125</v>
       </c>
@@ -12599,7 +12604,7 @@
       <c r="S45" s="7" t="s">
         <v>1</v>
       </c>
-      <c r="T45" s="40">
+      <c r="T45" s="85">
         <f>SUM(T29:T44)</f>
         <v>0.80054375</v>
       </c>
@@ -16274,7 +16279,7 @@
         <f t="shared" ref="J87:J102" si="7">INDEX($B$59:$D$64,MATCH($A87,$A$59:$A$64,0),MATCH($B87,$B$58:$D$58,0))</f>
         <v>50</v>
       </c>
-      <c r="K87" s="27">
+      <c r="K87" s="84">
         <f t="shared" ref="K87:K102" si="8">I87*J87</f>
         <v>0.16875</v>
       </c>
@@ -16364,7 +16369,7 @@
         <f t="shared" si="7"/>
         <v>100</v>
       </c>
-      <c r="K88" s="27">
+      <c r="K88" s="84">
         <f t="shared" si="8"/>
         <v>0.016</v>
       </c>
@@ -16454,7 +16459,7 @@
         <f t="shared" si="7"/>
         <v>30</v>
       </c>
-      <c r="K89" s="27">
+      <c r="K89" s="84">
         <f t="shared" si="8"/>
         <v>0.0192</v>
       </c>
@@ -16544,7 +16549,7 @@
         <f t="shared" si="7"/>
         <v>5</v>
       </c>
-      <c r="K90" s="27">
+      <c r="K90" s="84">
         <f t="shared" si="8"/>
         <v>0.016</v>
       </c>
@@ -16634,7 +16639,7 @@
         <f t="shared" si="7"/>
         <v>100</v>
       </c>
-      <c r="K91" s="27">
+      <c r="K91" s="84">
         <f t="shared" si="8"/>
         <v>0.024</v>
       </c>
@@ -16724,7 +16729,7 @@
         <f t="shared" si="7"/>
         <v>25</v>
       </c>
-      <c r="K92" s="27">
+      <c r="K92" s="84">
         <f t="shared" si="8"/>
         <v>0.024</v>
       </c>
@@ -16814,7 +16819,7 @@
         <f t="shared" si="7"/>
         <v>5</v>
       </c>
-      <c r="K93" s="27">
+      <c r="K93" s="84">
         <f t="shared" si="8"/>
         <v>0.024</v>
       </c>
@@ -16904,7 +16909,7 @@
         <f t="shared" si="7"/>
         <v>75</v>
       </c>
-      <c r="K94" s="27">
+      <c r="K94" s="84">
         <f t="shared" si="8"/>
         <v>0.0703125</v>
       </c>
@@ -16994,7 +16999,7 @@
         <f t="shared" si="7"/>
         <v>20</v>
       </c>
-      <c r="K95" s="27">
+      <c r="K95" s="84">
         <f t="shared" si="8"/>
         <v>0.05625</v>
       </c>
@@ -17084,7 +17089,7 @@
         <f t="shared" si="7"/>
         <v>5</v>
       </c>
-      <c r="K96" s="27">
+      <c r="K96" s="84">
         <f t="shared" si="8"/>
         <v>0.05625</v>
       </c>
@@ -17174,7 +17179,7 @@
         <f t="shared" si="7"/>
         <v>75</v>
       </c>
-      <c r="K97" s="27">
+      <c r="K97" s="84">
         <f t="shared" si="8"/>
         <v>0.05859375</v>
       </c>
@@ -17264,7 +17269,7 @@
         <f t="shared" si="7"/>
         <v>20</v>
       </c>
-      <c r="K98" s="27">
+      <c r="K98" s="84">
         <f t="shared" si="8"/>
         <v>0.046875</v>
       </c>
@@ -17354,7 +17359,7 @@
         <f t="shared" si="7"/>
         <v>5</v>
       </c>
-      <c r="K99" s="27">
+      <c r="K99" s="84">
         <f t="shared" si="8"/>
         <v>0.046875</v>
       </c>
@@ -17444,7 +17449,7 @@
         <f t="shared" si="7"/>
         <v>50</v>
       </c>
-      <c r="K100" s="27">
+      <c r="K100" s="84">
         <f t="shared" si="8"/>
         <v>0.0703125</v>
       </c>
@@ -17534,7 +17539,7 @@
         <f t="shared" si="7"/>
         <v>10</v>
       </c>
-      <c r="K101" s="27">
+      <c r="K101" s="84">
         <f t="shared" si="8"/>
         <v>0.0328125</v>
       </c>
@@ -17624,7 +17629,7 @@
         <f t="shared" si="7"/>
         <v>5</v>
       </c>
-      <c r="K102" s="27">
+      <c r="K102" s="84">
         <f t="shared" si="8"/>
         <v>0.0703125</v>
       </c>
@@ -17713,7 +17718,7 @@
       <c r="J103" s="7" t="s">
         <v>1</v>
       </c>
-      <c r="K103" s="40">
+      <c r="K103" s="85">
         <f>SUM(K87:K102)</f>
         <v>0.80054375</v>
       </c>
